--- a/04_DESIGN_TABLES/DesignTable_5601_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5601_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB7"/>
+  <dimension ref="A1:BB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,146 +686,146 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5601-02-02-02-FG</t>
+          <t>5601-06-06-06-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.78</v>
+        <v>1.22</v>
       </c>
       <c r="C2" t="n">
-        <v>0.281</v>
+        <v>0.4375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.19657</v>
+        <v>0.32823</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2639</v>
+        <v>0.4078</v>
       </c>
       <c r="F2" t="n">
         <v>1.7899</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1161</v>
+        <v>0.1522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.78</v>
+        <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.281</v>
+        <v>0.4375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19657</v>
+        <v>0.32823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2639</v>
+        <v>0.4078</v>
       </c>
       <c r="L2" t="n">
         <v>1.7899</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1161</v>
+        <v>0.1522</v>
       </c>
       <c r="N2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.66</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AP2" t="n">
         <v>0.66</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.39314</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.2639</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.03704</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.19657</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.16694</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.39314</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.2639</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.03704</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.19657</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.16694</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.03704</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.19463</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>5601-02-02-02-FG</t>
+          <t>5601-06-06-06-FG</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>Female Branch Pipe Tee, 1/8-27 NPTF x 1/8-27 NPTF x 1/8-27 NPTF (female)</t>
+          <t>Female Branch Pipe Tee, 3/8-18 NPTF x 3/8-18 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -835,17 +835,17 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -855,163 +855,163 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N1 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N2 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N3 LGTH" = "0.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A1 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A2 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_5601-06-06-06-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N1 LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1 (male): crossing to the tip; own STEP: +X face 1.22 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N2 LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2 (male): crossing to the tip; own STEP: -X face 1.22 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "N3 LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - branch (female port): crossing to the port face; own STEP: +Y face 1.02 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: A/F 0.875 on every leg (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "A1 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1 bore; own STEP: +X bore 0.406 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-06-06-06-FG col "A2 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 236.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2 bore; own STEP: -X bore 0.406 (C_ownstep/measure/5601-06-06-06-FG.txt (pipetee.py)); TAPDRILL@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.578); THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (this row: the drill MEASURED on its own Brennan STEP) from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 5601-6-6-6 (plain): N 1.22 / 1.22 / 1.02 W 0.88 D 0.41 / 0.41 TAPDRILL 0.57 (agrees to rounding)</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5601-02-02-02-FG</t>
+          <t>5601-06-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5601-04-04-04-FG</t>
+          <t>5601-02-02-02-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="F3" t="n">
         <v>1.7899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1582</v>
+        <v>0.1161</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="J3" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="L3" t="n">
         <v>1.7899</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1582</v>
+        <v>0.1161</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="O3" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="P3" t="n">
-        <v>0.281</v>
+        <v>0.188</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.281</v>
+        <v>0.188</v>
       </c>
       <c r="S3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="T3" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="V3" t="n">
-        <v>0.52183</v>
+        <v>0.39314</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.21647</v>
+        <v>0.16694</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.52183</v>
+        <v>0.39314</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.21647</v>
+        <v>0.16694</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.25944</v>
+        <v>0.19463</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>5601-04-04-04-FG</t>
+          <t>5601-02-02-02-FG</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>Female Branch Pipe Tee, 1/4-18 NPTF x 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Female Branch Pipe Tee, 1/8-27 NPTF x 1/8-27 NPTF x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>1/8-27 NPTF</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>1/8-27 NPTF</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1041,163 +1041,163 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N1 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N2 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N3 LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N1 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N2 LGTH" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "N3 LGTH" = "0.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A1 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-02-02-02-FG col "A2 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 216.7, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5601-04-04-04-FG</t>
+          <t>5601-02-02-02-FG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5601-08-08-08-FG</t>
+          <t>5601-04-04-04-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="C4" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="F4" t="n">
         <v>1.7899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2163</v>
+        <v>0.1582</v>
       </c>
       <c r="H4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="L4" t="n">
         <v>1.7899</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2163</v>
+        <v>0.1582</v>
       </c>
       <c r="N4" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="P4" t="n">
-        <v>0.531</v>
+        <v>0.281</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
-        <v>0.531</v>
+        <v>0.281</v>
       </c>
       <c r="S4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="U4" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="V4" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.40714</v>
+        <v>0.25944</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.23</v>
+        <v>0.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>5601-08-08-08-FG</t>
+          <t>5601-04-04-04-FG</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Female Branch Pipe Tee, 1/2-14 NPTF x 1/2-14 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Female Branch Pipe Tee, 1/4-18 NPTF x 1/4-18 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1227,163 +1227,163 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / drills from the Brennan TFA catalog p.55; tap drill = Air-Way per size (A1); NPTF majors ASME | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N1 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N2 LGTH" = "1.09" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "N3 LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-04-04-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 226.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.55 alone; marked DimSource BRENNAN</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5601-08-08-08-FG</t>
+          <t>5601-04-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5601-12-12-12-FG</t>
+          <t>5601-08-08-08-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="C5" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="D5" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="F5" t="n">
         <v>1.7899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="H5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="I5" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="J5" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="L5" t="n">
         <v>1.7899</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="O5" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="P5" t="n">
-        <v>0.719</v>
+        <v>0.531</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>0.719</v>
+        <v>0.531</v>
       </c>
       <c r="S5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="X5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="AD5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.51214</v>
+        <v>0.40714</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.312</v>
+        <v>1.062</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.312</v>
+        <v>1.062</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>5601-12-12-12-FG</t>
+          <t>5601-08-08-08-FG</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Female Branch Pipe Tee, 3/4-14 NPTF x 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Female Branch Pipe Tee, 1/2-14 NPTF x 1/2-14 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1423,153 +1423,153 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5601-12-12-12-FG</t>
+          <t>5601-08-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5601-16-16-16-FG</t>
+          <t>5601-12-12-12-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="F6" t="n">
         <v>1.7899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="L6" t="n">
         <v>1.7899</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8125</v>
+        <v>0.656</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="S6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="T6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.63957</v>
+        <v>0.51214</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.625</v>
+        <v>1.312</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.625</v>
+        <v>1.312</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>5601-16-16-16-FG</t>
+          <t>5601-12-12-12-FG</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Female Branch Pipe Tee, 1-11 1/2 NPTF x 1-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Female Branch Pipe Tee, 3/4-14 NPTF x 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1609,191 +1609,377 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5601-16-16-16-FG</t>
+          <t>5601-12-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5601-20-20-20-FG</t>
+          <t>5601-16-16-16-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="D7" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="F7" t="n">
         <v>1.7899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="L7" t="n">
         <v>1.7899</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="X7" t="n">
         <v>0.08696</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="AD7" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08696</v>
       </c>
       <c r="AK7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>5601-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Female Branch Pipe Tee, 1-11 1/2 NPTF x 1-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>5601</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / drills from the Brennan TFA catalog p.55; tap drill = Air-Way per size (A1); NPTF majors ASME | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.55 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>5601-16-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5601-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AK8" t="n">
         <v>0.74</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AL8" t="n">
         <v>0.80957</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AM8" t="n">
         <v>1.7</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN8" t="n">
         <v>1.875</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO8" t="n">
         <v>1.41</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP8" t="n">
         <v>1.41</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ8" t="n">
         <v>1.875</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR8" t="n">
         <v>1.44</v>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>5601-20-20-20-FG</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>Female Branch Pipe Tee, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>5601</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N_1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N1 LGTH" = "2.38" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N2@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N2 LGTH" = "2.38" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1@DRIVE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "N3 LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "Y FLATS" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D1@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); D2@BORE: Brennan TFA catalog p.55 table TFA-p055-t02 "5601-FG MP-MP-FP TEE (AS CODED PER SAE J846)" row 5601-20-20-20-FG col "A2 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 277.2, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(the row W, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; CONFIRMED on the Brennan 5601-06-06-06-FG pilot STEP (tools/measure/pipetee.py 2026-10-02, validated on Brennan 5605-08-08-08-FG and 5600-16-16-16-FG): hex to 0.26 short of a female face (round collar) / to the 5404 end length of a male leg, flat hex ends with no chamfer and no edge fillet (the STEP has plane, cylinder and cone faces only); the 0.002-deep marks on its hex flats near the crossing are NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); male legs = the library NPTFM end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): on the Brennan 5601-06-06-06-FG pilot STEP the hex stops at the 5404 end length and the bore of the row's drill column runs from the tip to the crossing (= the model); Brennan's relief ring at the pipe OD (0.03-0.04 long), its simplified thread cone, the 45deg tip chamfer and the 30deg bore-mouth countersink are NOT modelled (ASSUMPTION); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer; the Brennan 5601-06-06-06-FG pilot STEP too: collar 0.260 on every female leg); port-mouth 45deg chamfer not modelled; female NPTF legs = the library NPTFF end (end shape NOT taken from the pilot STEP, as on the accepted 5600 / 5602 / 5604 / 5605 masters - user decision Q-TRANSFER-ENDLIB open): a drill of the row TAPDRILL (its source: this row's cell sources before ' | MODEL:') from the port face to the axis crossing - on the Brennan 5601-06-06-06-FG pilot STEP the drill runs from the bottom of the tapered port to the crossing, so no separate connecting drill; helical NPTF thread over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)); the pilot's port taper (1.79deg, 0.580 deep, shorter than P1) and its 45deg mouth chamfer are NOT modelled (ASSUMPTION: the thread representation of the library NPTFF end); each leg bore runs from its face to the axis crossing; leg 3: the helical NPTF thread (MS51503 P1 1.160 from the face) ends 0.540 from the axis crossing, 0.085 inside the perpendicular bore (radius 0.6250): it runs out into the cross hole (ASSUMPTION; drawing-only thread, suppressed in the saved model and STEP)</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>5601-20-20-20-FG</t>
         </is>
